--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="59">
   <si>
     <t>Дата</t>
   </si>
@@ -53,33 +53,6 @@
   </si>
   <si>
     <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>2026-05-05</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-05-09</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>2026-05-12</t>
-  </si>
-  <si>
-    <t>2026-05-13</t>
-  </si>
-  <si>
-    <t>2026-05-14</t>
   </si>
   <si>
     <t>В4837НР</t>
@@ -224,8 +197,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -311,11 +285,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -323,9 +298,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -679,20 +654,20 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
+      <c r="A2" s="2">
+        <v>46146</v>
       </c>
       <c r="B2">
         <v>1146</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F2">
         <v>37.671</v>
@@ -710,7 +685,7 @@
         <v>57.26</v>
       </c>
       <c r="K2" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -720,20 +695,20 @@
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>13</v>
+      <c r="A3" s="2">
+        <v>46146</v>
       </c>
       <c r="B3">
         <v>1148</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F3">
         <v>115</v>
@@ -751,7 +726,7 @@
         <v>207</v>
       </c>
       <c r="K3" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -761,20 +736,20 @@
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>14</v>
+      <c r="A4" s="2">
+        <v>46147</v>
       </c>
       <c r="B4">
         <v>1146</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F4">
         <v>20</v>
@@ -792,7 +767,7 @@
         <v>30.4</v>
       </c>
       <c r="K4" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -802,20 +777,20 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>14</v>
+      <c r="A5" s="2">
+        <v>46147</v>
       </c>
       <c r="B5">
         <v>1146</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F5">
         <v>33.494</v>
@@ -833,7 +808,7 @@
         <v>27.8</v>
       </c>
       <c r="K5" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -843,20 +818,20 @@
       </c>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" t="s">
-        <v>14</v>
+      <c r="A6" s="2">
+        <v>46147</v>
       </c>
       <c r="B6">
         <v>1146</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F6">
         <v>109.622</v>
@@ -874,7 +849,7 @@
         <v>197.32</v>
       </c>
       <c r="K6" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -884,20 +859,20 @@
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" t="s">
-        <v>15</v>
+      <c r="A7" s="2">
+        <v>46149</v>
       </c>
       <c r="B7">
         <v>1148</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F7">
         <v>117.578</v>
@@ -915,7 +890,7 @@
         <v>211.64</v>
       </c>
       <c r="K7" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -925,20 +900,20 @@
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" t="s">
-        <v>16</v>
+      <c r="A8" s="2">
+        <v>46150</v>
       </c>
       <c r="B8">
         <v>1148</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F8">
         <v>33.32</v>
@@ -956,7 +931,7 @@
         <v>50.98</v>
       </c>
       <c r="K8" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -966,20 +941,20 @@
       </c>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" t="s">
-        <v>17</v>
+      <c r="A9" s="2">
+        <v>46151</v>
       </c>
       <c r="B9">
         <v>1148</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F9">
         <v>117.581</v>
@@ -997,7 +972,7 @@
         <v>210.47</v>
       </c>
       <c r="K9" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -1007,20 +982,20 @@
       </c>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" t="s">
-        <v>18</v>
+      <c r="A10" s="2">
+        <v>46153</v>
       </c>
       <c r="B10">
         <v>1148</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F10">
         <v>100.749</v>
@@ -1038,7 +1013,7 @@
         <v>180.34</v>
       </c>
       <c r="K10" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -1048,20 +1023,20 @@
       </c>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" t="s">
-        <v>18</v>
+      <c r="A11" s="2">
+        <v>46153</v>
       </c>
       <c r="B11">
         <v>1158</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E11" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F11">
         <v>45</v>
@@ -1079,7 +1054,7 @@
         <v>69.3</v>
       </c>
       <c r="K11" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -1089,20 +1064,20 @@
       </c>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" t="s">
-        <v>19</v>
+      <c r="A12" s="2">
+        <v>46154</v>
       </c>
       <c r="B12">
         <v>1146</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E12" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F12">
         <v>10</v>
@@ -1120,7 +1095,7 @@
         <v>15.4</v>
       </c>
       <c r="K12" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1130,20 +1105,20 @@
       </c>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" t="s">
-        <v>19</v>
+      <c r="A13" s="2">
+        <v>46154</v>
       </c>
       <c r="B13">
         <v>1148</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E13" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F13">
         <v>120</v>
@@ -1161,7 +1136,7 @@
         <v>214.8</v>
       </c>
       <c r="K13" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1171,20 +1146,20 @@
       </c>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" t="s">
-        <v>20</v>
+      <c r="A14" s="2">
+        <v>46155</v>
       </c>
       <c r="B14">
         <v>1148</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E14" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F14">
         <v>36.688</v>
@@ -1202,7 +1177,7 @@
         <v>56.5</v>
       </c>
       <c r="K14" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -1212,20 +1187,20 @@
       </c>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" t="s">
-        <v>21</v>
+      <c r="A15" s="2">
+        <v>46156</v>
       </c>
       <c r="B15">
         <v>1148</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D15" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E15" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F15">
         <v>109.35</v>
@@ -1243,7 +1218,7 @@
         <v>193.55</v>
       </c>
       <c r="K15" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -1253,126 +1228,126 @@
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
+      <c r="A18" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>66</v>
+      <c r="A19" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B20" s="5">
+      <c r="A20" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="6">
         <v>789.88</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="6">
         <v>7</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="6">
         <v>1.7616</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="6">
         <v>1391.42</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="6">
         <v>1415.12</v>
       </c>
-      <c r="G20" s="5">
+      <c r="G20" s="6">
         <v>23.7</v>
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21" s="5">
+      <c r="A21" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="6">
         <v>182.679</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="6">
         <v>6</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="6">
         <v>1.5019</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="6">
         <v>274.36</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21" s="6">
         <v>279.84</v>
       </c>
-      <c r="G21" s="5">
+      <c r="G21" s="6">
         <v>5.48</v>
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22" s="5">
+      <c r="A22" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="6">
         <v>33.494</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="6">
         <v>1</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="6">
         <v>0.8201000000000001</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="6">
         <v>27.47</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F22" s="6">
         <v>27.8</v>
       </c>
-      <c r="G22" s="5">
+      <c r="G22" s="6">
         <v>0.33</v>
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="B23" s="7">
+      <c r="A23" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" s="8">
         <v>1006.053</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="8">
         <v>14</v>
       </c>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7">
+      <c r="D23" s="8"/>
+      <c r="E23" s="8">
         <v>1693.25</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="8">
         <v>1722.76</v>
       </c>
-      <c r="G23" s="7">
+      <c r="G23" s="8">
         <v>29.51</v>
       </c>
     </row>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА.xlsx
@@ -269,7 +269,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -279,12 +279,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -335,17 +329,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="59">
   <si>
     <t>Дата</t>
   </si>
@@ -46,9 +46,15 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
+    <t>Час</t>
+  </si>
+  <si>
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>Варна Порт</t>
   </si>
   <si>
@@ -116,6 +122,57 @@
   </si>
   <si>
     <t>E GAS LPG</t>
+  </si>
+  <si>
+    <t>10:56</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>09:21</t>
+  </si>
+  <si>
+    <t>09:31</t>
+  </si>
+  <si>
+    <t>09:33</t>
+  </si>
+  <si>
+    <t>12:59</t>
+  </si>
+  <si>
+    <t>11:22</t>
+  </si>
+  <si>
+    <t>13:56</t>
+  </si>
+  <si>
+    <t>18:36</t>
+  </si>
+  <si>
+    <t>18:39</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>12:08</t>
+  </si>
+  <si>
+    <t>12:24</t>
+  </si>
+  <si>
+    <t>15:11</t>
+  </si>
+  <si>
+    <t>12:31</t>
+  </si>
+  <si>
+    <t>16:56</t>
+  </si>
+  <si>
+    <t>17:29</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА</t>
@@ -535,7 +592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -548,10 +605,12 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -585,22 +644,28 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46175</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F2">
         <v>109</v>
@@ -617,25 +682,31 @@
       <c r="J2">
         <v>184.21</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L2">
         <v>245541</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="M2">
+        <v>213886</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46175</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F3">
         <v>37.97</v>
@@ -652,25 +723,31 @@
       <c r="J3">
         <v>59.61</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3">
         <v>62275</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="M3">
+        <v>213971</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46177</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F4">
         <v>115.72</v>
@@ -687,25 +764,31 @@
       <c r="J4">
         <v>192.1</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L4">
         <v>131332</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="M4">
+        <v>214665</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
         <v>46177</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F5">
         <v>29.01</v>
@@ -722,25 +805,31 @@
       <c r="J5">
         <v>21.47</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="s">
+        <v>39</v>
+      </c>
+      <c r="L5">
         <v>230570</v>
       </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="M5">
+        <v>214670</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="3">
         <v>46177</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F6">
         <v>36.36</v>
@@ -757,25 +846,31 @@
       <c r="J6">
         <v>57.09</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="s">
+        <v>40</v>
+      </c>
+      <c r="L6">
         <v>60750</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="M6">
+        <v>214672</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="3">
         <v>46177</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F7">
         <v>115</v>
@@ -792,25 +887,31 @@
       <c r="J7">
         <v>190.9</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="s">
+        <v>41</v>
+      </c>
+      <c r="L7">
         <v>127770</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="M7">
+        <v>214781</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="3">
         <v>46178</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F8">
         <v>43.31</v>
@@ -827,25 +928,31 @@
       <c r="J8">
         <v>68</v>
       </c>
-      <c r="K8">
+      <c r="K8" t="s">
+        <v>42</v>
+      </c>
+      <c r="L8">
         <v>74080</v>
       </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="M8">
+        <v>215160</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="3">
         <v>46182</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F9">
         <v>35.01</v>
@@ -862,25 +969,31 @@
       <c r="J9">
         <v>54.62</v>
       </c>
-      <c r="K9">
+      <c r="K9" t="s">
+        <v>43</v>
+      </c>
+      <c r="L9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="M9">
+        <v>140284</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="3">
         <v>46182</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F10">
         <v>114.7</v>
@@ -897,25 +1010,31 @@
       <c r="J10">
         <v>188.11</v>
       </c>
-      <c r="K10">
+      <c r="K10" t="s">
+        <v>44</v>
+      </c>
+      <c r="L10">
         <v>128160</v>
       </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="M10">
+        <v>216970</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="3">
         <v>46182</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F11">
         <v>118</v>
@@ -932,25 +1051,31 @@
       <c r="J11">
         <v>193.52</v>
       </c>
-      <c r="K11">
+      <c r="K11" t="s">
+        <v>45</v>
+      </c>
+      <c r="L11">
         <v>131784</v>
       </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="M11">
+        <v>216972</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="3">
         <v>46183</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F12">
         <v>108</v>
@@ -967,25 +1092,31 @@
       <c r="J12">
         <v>176.04</v>
       </c>
-      <c r="K12">
+      <c r="K12" t="s">
+        <v>46</v>
+      </c>
+      <c r="L12">
         <v>246057</v>
       </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="M12">
+        <v>217113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="3">
         <v>46185</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F13">
         <v>28.52</v>
@@ -1002,25 +1133,31 @@
       <c r="J13">
         <v>19.39</v>
       </c>
-      <c r="K13">
+      <c r="K13" t="s">
+        <v>47</v>
+      </c>
+      <c r="L13">
         <v>230732</v>
       </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="M13">
+        <v>218178</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="3">
         <v>46187</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F14">
         <v>120.48</v>
@@ -1037,25 +1174,31 @@
       <c r="J14">
         <v>192.77</v>
       </c>
-      <c r="K14">
+      <c r="K14" t="s">
+        <v>48</v>
+      </c>
+      <c r="L14">
         <v>132184</v>
       </c>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="M14">
+        <v>218933</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="3">
         <v>46187</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F15">
         <v>117.62</v>
@@ -1072,25 +1215,31 @@
       <c r="J15">
         <v>188.19</v>
       </c>
-      <c r="K15">
+      <c r="K15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15">
         <v>128552</v>
       </c>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="M15">
+        <v>219010</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="3">
         <v>46188</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D16" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F16">
         <v>36.57</v>
@@ -1107,25 +1256,31 @@
       <c r="J16">
         <v>57.05</v>
       </c>
-      <c r="K16">
+      <c r="K16" t="s">
+        <v>50</v>
+      </c>
+      <c r="L16">
         <v>62745</v>
       </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="M16">
+        <v>219344</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="3">
         <v>46188</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F17">
         <v>32.6</v>
@@ -1142,25 +1297,31 @@
       <c r="J17">
         <v>50.86</v>
       </c>
-      <c r="K17">
+      <c r="K17" t="s">
+        <v>51</v>
+      </c>
+      <c r="L17">
         <v>61641</v>
       </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="M17">
+        <v>219505</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="3">
         <v>46188</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E18" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F18">
         <v>110.98</v>
@@ -1177,13 +1338,19 @@
       <c r="J18">
         <v>177.57</v>
       </c>
-      <c r="K18">
+      <c r="K18" t="s">
+        <v>52</v>
+      </c>
+      <c r="L18">
         <v>246554</v>
       </c>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="M18">
+        <v>219531</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="4" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -1191,18 +1358,18 @@
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:13">
       <c r="A22" s="5" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>7</v>
@@ -1211,9 +1378,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:13">
       <c r="A23" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B23" s="7">
         <v>1029.5</v>
@@ -1231,9 +1398,9 @@
         <v>1683.41</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:13">
       <c r="A24" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B24" s="7">
         <v>221.82</v>
@@ -1251,9 +1418,9 @@
         <v>347.23</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:13">
       <c r="A25" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B25" s="7">
         <v>57.53</v>
@@ -1271,9 +1438,9 @@
         <v>40.86</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:13">
       <c r="A26" s="9" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="B26" s="10">
         <v>1308.85</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="81">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,18 +52,24 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Варна Порт</t>
-  </si>
-  <si>
-    <t>Варна Сливница</t>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>В2881РХ</t>
   </si>
   <si>
     <t>В4837НР</t>
   </si>
   <si>
-    <t>В2881РХ</t>
-  </si>
-  <si>
     <t>В4291НТ</t>
   </si>
   <si>
@@ -79,12 +88,18 @@
     <t>В4792НР</t>
   </si>
   <si>
+    <t>В4839НР</t>
+  </si>
+  <si>
+    <t>В4835НР</t>
+  </si>
+  <si>
+    <t>78970155027721871</t>
+  </si>
+  <si>
     <t>78970155027721830</t>
   </si>
   <si>
-    <t>78970155027721871</t>
-  </si>
-  <si>
     <t>78970155027721947</t>
   </si>
   <si>
@@ -103,6 +118,12 @@
     <t>78970155027721863</t>
   </si>
   <si>
+    <t>78970155027721848</t>
+  </si>
+  <si>
+    <t>78970155027721822</t>
+  </si>
+  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
@@ -112,34 +133,112 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>2026-06-16 09:52:13</t>
-  </si>
-  <si>
-    <t>2026-06-16 13:06:27</t>
-  </si>
-  <si>
-    <t>2026-06-18 12:10:23</t>
-  </si>
-  <si>
-    <t>2026-06-18 13:56:49</t>
-  </si>
-  <si>
-    <t>2026-06-22 09:18:42</t>
-  </si>
-  <si>
-    <t>2026-06-22 09:57:09</t>
-  </si>
-  <si>
-    <t>2026-06-22 10:05:56</t>
-  </si>
-  <si>
-    <t>2026-06-23 08:38:42</t>
-  </si>
-  <si>
-    <t>2026-06-23 09:14:29</t>
-  </si>
-  <si>
-    <t>2026-06-23 10:00:43</t>
+    <t>DIESEL DOUBLE FILTERED</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>13:06:00</t>
+  </si>
+  <si>
+    <t>09:52:00</t>
+  </si>
+  <si>
+    <t>12:10:00</t>
+  </si>
+  <si>
+    <t>13:56:00</t>
+  </si>
+  <si>
+    <t>09:18:00</t>
+  </si>
+  <si>
+    <t>10:06:00</t>
+  </si>
+  <si>
+    <t>09:57:00</t>
+  </si>
+  <si>
+    <t>08:39:00</t>
+  </si>
+  <si>
+    <t>09:14:00</t>
+  </si>
+  <si>
+    <t>10:00:00</t>
+  </si>
+  <si>
+    <t>11:09:00</t>
+  </si>
+  <si>
+    <t>12:37:00</t>
+  </si>
+  <si>
+    <t>17:26:00</t>
+  </si>
+  <si>
+    <t>19:02:00</t>
+  </si>
+  <si>
+    <t>17:06:00</t>
+  </si>
+  <si>
+    <t>15:30:00</t>
+  </si>
+  <si>
+    <t>15:37:00</t>
+  </si>
+  <si>
+    <t>3233420174 3233420174</t>
+  </si>
+  <si>
+    <t>3233435407 3233435407</t>
+  </si>
+  <si>
+    <t>3233531270 3233531270</t>
+  </si>
+  <si>
+    <t>3233535916 3233535916</t>
+  </si>
+  <si>
+    <t>3233718186 3233718186</t>
+  </si>
+  <si>
+    <t>3233719927 3233719927</t>
+  </si>
+  <si>
+    <t>3233720215 3233720215</t>
+  </si>
+  <si>
+    <t>3233748012 3233748012</t>
+  </si>
+  <si>
+    <t>3233764569 3233764569</t>
+  </si>
+  <si>
+    <t>3233767105 3233767105</t>
+  </si>
+  <si>
+    <t>3233936659 3233936659</t>
+  </si>
+  <si>
+    <t>3233937870 3233937870</t>
+  </si>
+  <si>
+    <t>3233948161 3233948161</t>
+  </si>
+  <si>
+    <t>3233968150 3233968150</t>
+  </si>
+  <si>
+    <t>3234066541 3234066541</t>
+  </si>
+  <si>
+    <t>3234029844 3234029844</t>
+  </si>
+  <si>
+    <t>3234110194 3234110194</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА</t>
@@ -559,7 +658,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -568,14 +667,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -609,468 +711,895 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46189</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F2">
-        <v>36.64</v>
-      </c>
-      <c r="G2" s="1">
+        <v>55.01</v>
+      </c>
+      <c r="G2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2">
         <v>1.53</v>
       </c>
-      <c r="H2">
-        <v>56.06</v>
-      </c>
       <c r="I2" s="1">
+        <v>84.17</v>
+      </c>
+      <c r="J2">
         <v>1.56</v>
       </c>
-      <c r="J2">
-        <v>57.16</v>
-      </c>
-      <c r="K2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="K2" s="1">
+        <v>85.81999999999999</v>
+      </c>
+      <c r="L2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2">
+        <v>375195</v>
+      </c>
+      <c r="N2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46189</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F3">
-        <v>55.01</v>
-      </c>
-      <c r="G3" s="1">
+        <v>36.64</v>
+      </c>
+      <c r="G3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3">
         <v>1.53</v>
       </c>
-      <c r="H3">
-        <v>84.17</v>
-      </c>
       <c r="I3" s="1">
+        <v>56.06</v>
+      </c>
+      <c r="J3">
         <v>1.56</v>
       </c>
-      <c r="J3">
-        <v>85.81999999999999</v>
-      </c>
-      <c r="K3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="K3" s="1">
+        <v>57.16</v>
+      </c>
+      <c r="L3" t="s">
+        <v>42</v>
+      </c>
+      <c r="M3">
+        <v>61250</v>
+      </c>
+      <c r="N3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46191</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F4">
         <v>115</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4">
         <v>1.55</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>178.25</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.58</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>181.7</v>
       </c>
-      <c r="K4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4" t="s">
+        <v>43</v>
+      </c>
+      <c r="M4">
+        <v>128922</v>
+      </c>
+      <c r="N4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46191</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F5">
         <v>114.16</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5">
         <v>1.55</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>176.95</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.58</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>180.37</v>
       </c>
-      <c r="K5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5" t="s">
+        <v>44</v>
+      </c>
+      <c r="M5">
+        <v>132553</v>
+      </c>
+      <c r="N5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
         <v>46195</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F6">
         <v>89.89</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6">
         <v>1.49</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>133.94</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.52</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>136.63</v>
       </c>
-      <c r="K6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6" t="s">
+        <v>45</v>
+      </c>
+      <c r="M6">
+        <v>246997</v>
+      </c>
+      <c r="N6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
         <v>46195</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F7">
-        <v>32.47</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0.65</v>
+        <v>106.55</v>
+      </c>
+      <c r="G7" t="s">
+        <v>40</v>
       </c>
       <c r="H7">
-        <v>21.11</v>
+        <v>1.49</v>
       </c>
       <c r="I7" s="1">
-        <v>0.66</v>
+        <v>158.76</v>
       </c>
       <c r="J7">
-        <v>21.43</v>
-      </c>
-      <c r="K7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+        <v>1.52</v>
+      </c>
+      <c r="K7" s="1">
+        <v>161.96</v>
+      </c>
+      <c r="L7" t="s">
+        <v>46</v>
+      </c>
+      <c r="M7">
+        <v>129275</v>
+      </c>
+      <c r="N7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="3">
         <v>46195</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F8">
-        <v>106.55</v>
-      </c>
-      <c r="G8" s="1">
-        <v>1.49</v>
+        <v>32.47</v>
+      </c>
+      <c r="G8" t="s">
+        <v>40</v>
       </c>
       <c r="H8">
-        <v>158.76</v>
+        <v>0.65</v>
       </c>
       <c r="I8" s="1">
-        <v>1.52</v>
+        <v>21.11</v>
       </c>
       <c r="J8">
-        <v>161.96</v>
-      </c>
-      <c r="K8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+        <v>0.66</v>
+      </c>
+      <c r="K8" s="1">
+        <v>21.43</v>
+      </c>
+      <c r="L8" t="s">
+        <v>47</v>
+      </c>
+      <c r="M8">
+        <v>230921</v>
+      </c>
+      <c r="N8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="3">
         <v>46196</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F9">
         <v>36.35</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9">
         <v>1.48</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="1">
         <v>53.8</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>1.51</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>54.89</v>
       </c>
-      <c r="K9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="L9" t="s">
+        <v>48</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="3">
         <v>46196</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F10">
         <v>113.03</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10">
         <v>1.49</v>
       </c>
-      <c r="H10">
+      <c r="I10" s="1">
         <v>168.41</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10">
         <v>1.52</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="1">
         <v>171.81</v>
       </c>
-      <c r="K10" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="L10" t="s">
+        <v>49</v>
+      </c>
+      <c r="M10">
+        <v>132950</v>
+      </c>
+      <c r="N10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="3">
         <v>46196</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F11">
         <v>43.95</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11">
         <v>1.48</v>
       </c>
-      <c r="H11">
+      <c r="I11" s="1">
         <v>65.05</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11">
         <v>1.51</v>
       </c>
-      <c r="J11">
+      <c r="K11" s="1">
         <v>66.36</v>
       </c>
-      <c r="K11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E15" s="5" t="s">
+      <c r="L11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11">
+        <v>74566</v>
+      </c>
+      <c r="N11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12">
+        <v>33.61</v>
+      </c>
+      <c r="G12" t="s">
+        <v>40</v>
+      </c>
+      <c r="H12">
+        <v>0.65</v>
+      </c>
+      <c r="I12" s="1">
+        <v>21.85</v>
+      </c>
+      <c r="J12">
+        <v>0.66</v>
+      </c>
+      <c r="K12" s="1">
+        <v>22.18</v>
+      </c>
+      <c r="L12" t="s">
+        <v>51</v>
+      </c>
+      <c r="M12">
+        <v>231080</v>
+      </c>
+      <c r="N12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13">
+        <v>103.6</v>
+      </c>
+      <c r="G13" t="s">
+        <v>40</v>
+      </c>
+      <c r="H13">
+        <v>1.48</v>
+      </c>
+      <c r="I13" s="1">
+        <v>153.33</v>
+      </c>
+      <c r="J13">
+        <v>1.51</v>
+      </c>
+      <c r="K13" s="1">
+        <v>156.44</v>
+      </c>
+      <c r="L13" t="s">
+        <v>52</v>
+      </c>
+      <c r="M13">
+        <v>129611</v>
+      </c>
+      <c r="N13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14">
+        <v>99.39</v>
+      </c>
+      <c r="G14" t="s">
+        <v>40</v>
+      </c>
+      <c r="H14">
+        <v>1.74</v>
+      </c>
+      <c r="I14" s="1">
+        <v>172.94</v>
+      </c>
+      <c r="J14">
+        <v>1.77</v>
+      </c>
+      <c r="K14" s="1">
+        <v>175.92</v>
+      </c>
+      <c r="L14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M14">
+        <v>133283</v>
+      </c>
+      <c r="N14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="3">
+        <v>46200</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15">
+        <v>97.47</v>
+      </c>
+      <c r="G15" t="s">
+        <v>40</v>
+      </c>
+      <c r="H15">
+        <v>1.48</v>
+      </c>
+      <c r="I15" s="1">
+        <v>144.26</v>
+      </c>
+      <c r="J15">
+        <v>1.51</v>
+      </c>
+      <c r="K15" s="1">
+        <v>147.18</v>
+      </c>
+      <c r="L15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M15">
+        <v>247458</v>
+      </c>
+      <c r="N15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16">
+        <v>33.33</v>
+      </c>
+      <c r="G16" t="s">
+        <v>40</v>
+      </c>
+      <c r="H16">
+        <v>1.47</v>
+      </c>
+      <c r="I16" s="1">
+        <v>49</v>
+      </c>
+      <c r="J16">
+        <v>1.5</v>
+      </c>
+      <c r="K16" s="1">
+        <v>50</v>
+      </c>
+      <c r="L16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M16">
+        <v>63150</v>
+      </c>
+      <c r="N16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F17">
+        <v>36.46</v>
+      </c>
+      <c r="G17" t="s">
+        <v>40</v>
+      </c>
+      <c r="H17">
+        <v>1.47</v>
+      </c>
+      <c r="I17" s="1">
+        <v>53.6</v>
+      </c>
+      <c r="J17">
+        <v>1.5</v>
+      </c>
+      <c r="K17" s="1">
+        <v>54.69</v>
+      </c>
+      <c r="L17" t="s">
+        <v>56</v>
+      </c>
+      <c r="M17">
+        <v>61770</v>
+      </c>
+      <c r="N17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18">
+        <v>35.07</v>
+      </c>
+      <c r="G18" t="s">
+        <v>40</v>
+      </c>
+      <c r="H18">
+        <v>1.47</v>
+      </c>
+      <c r="I18" s="1">
+        <v>51.55</v>
+      </c>
+      <c r="J18">
+        <v>1.5</v>
+      </c>
+      <c r="K18" s="1">
+        <v>52.6</v>
+      </c>
+      <c r="L18" t="s">
+        <v>57</v>
+      </c>
+      <c r="M18">
+        <v>62052</v>
+      </c>
+      <c r="N18" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="7">
+        <v>739.7</v>
+      </c>
+      <c r="C23" s="7">
         <v>7</v>
       </c>
-      <c r="F15" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="7">
-        <v>538.63</v>
-      </c>
-      <c r="C16" s="7">
-        <v>5</v>
-      </c>
-      <c r="D16" s="8">
-        <v>1.5155</v>
-      </c>
-      <c r="E16" s="7">
-        <v>816.3099999999999</v>
-      </c>
-      <c r="F16" s="7">
-        <v>832.47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="7">
-        <v>171.95</v>
-      </c>
-      <c r="C17" s="7">
-        <v>4</v>
-      </c>
-      <c r="D17" s="8">
-        <v>1.5067</v>
-      </c>
-      <c r="E17" s="7">
-        <v>259.08</v>
-      </c>
-      <c r="F17" s="7">
-        <v>264.23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" s="7">
-        <v>32.47</v>
-      </c>
-      <c r="C18" s="7">
+      <c r="D23" s="8">
+        <v>1.5059</v>
+      </c>
+      <c r="E23" s="7">
+        <v>1113.9</v>
+      </c>
+      <c r="F23" s="7">
+        <v>1136.09</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="7">
+        <v>276.81</v>
+      </c>
+      <c r="C24" s="7">
+        <v>7</v>
+      </c>
+      <c r="D24" s="8">
+        <v>1.4928</v>
+      </c>
+      <c r="E24" s="7">
+        <v>413.23</v>
+      </c>
+      <c r="F24" s="7">
+        <v>421.52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="7">
+        <v>99.39</v>
+      </c>
+      <c r="C25" s="7">
         <v>1</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D25" s="8">
+        <v>1.74</v>
+      </c>
+      <c r="E25" s="7">
+        <v>172.94</v>
+      </c>
+      <c r="F25" s="7">
+        <v>175.92</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="7">
+        <v>66.08</v>
+      </c>
+      <c r="C26" s="7">
+        <v>2</v>
+      </c>
+      <c r="D26" s="8">
         <v>0.6501</v>
       </c>
-      <c r="E18" s="7">
-        <v>21.11</v>
-      </c>
-      <c r="F18" s="7">
-        <v>21.43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B19" s="10">
-        <v>743.05</v>
-      </c>
-      <c r="C19" s="10">
-        <v>10</v>
-      </c>
-      <c r="D19" s="8"/>
-      <c r="E19" s="10">
-        <v>1096.5</v>
-      </c>
-      <c r="F19" s="10">
-        <v>1118.13</v>
+      <c r="E26" s="7">
+        <v>42.96</v>
+      </c>
+      <c r="F26" s="7">
+        <v>43.61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B27" s="10">
+        <v>1181.98</v>
+      </c>
+      <c r="C27" s="10">
+        <v>17</v>
+      </c>
+      <c r="D27" s="8"/>
+      <c r="E27" s="10">
+        <v>1743.03</v>
+      </c>
+      <c r="F27" s="10">
+        <v>1777.14</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="62">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,18 +55,18 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1146 Варна Сливница</t>
-  </si>
-  <si>
-    <t>1148 Варна пристанище</t>
+    <t>Варна Порт</t>
+  </si>
+  <si>
+    <t>Варна Сливница</t>
+  </si>
+  <si>
+    <t>В4837НР</t>
   </si>
   <si>
     <t>В2881РХ</t>
   </si>
   <si>
-    <t>В4837НР</t>
-  </si>
-  <si>
     <t>В4291НТ</t>
   </si>
   <si>
@@ -94,12 +91,12 @@
     <t>В4835НР</t>
   </si>
   <si>
+    <t>78970155027721830</t>
+  </si>
+  <si>
     <t>78970155027721871</t>
   </si>
   <si>
-    <t>78970155027721830</t>
-  </si>
-  <si>
     <t>78970155027721947</t>
   </si>
   <si>
@@ -133,112 +130,58 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>DIESEL DOUBLE FILTERED</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>13:06:00</t>
-  </si>
-  <si>
-    <t>09:52:00</t>
-  </si>
-  <si>
-    <t>12:10:00</t>
-  </si>
-  <si>
-    <t>13:56:00</t>
-  </si>
-  <si>
-    <t>09:18:00</t>
-  </si>
-  <si>
-    <t>10:06:00</t>
-  </si>
-  <si>
-    <t>09:57:00</t>
-  </si>
-  <si>
-    <t>08:39:00</t>
-  </si>
-  <si>
-    <t>09:14:00</t>
-  </si>
-  <si>
-    <t>10:00:00</t>
-  </si>
-  <si>
-    <t>11:09:00</t>
-  </si>
-  <si>
-    <t>12:37:00</t>
-  </si>
-  <si>
-    <t>17:26:00</t>
-  </si>
-  <si>
-    <t>19:02:00</t>
-  </si>
-  <si>
-    <t>17:06:00</t>
-  </si>
-  <si>
-    <t>15:30:00</t>
-  </si>
-  <si>
-    <t>15:37:00</t>
-  </si>
-  <si>
-    <t>3233420174 3233420174</t>
-  </si>
-  <si>
-    <t>3233435407 3233435407</t>
-  </si>
-  <si>
-    <t>3233531270 3233531270</t>
-  </si>
-  <si>
-    <t>3233535916 3233535916</t>
-  </si>
-  <si>
-    <t>3233718186 3233718186</t>
-  </si>
-  <si>
-    <t>3233719927 3233719927</t>
-  </si>
-  <si>
-    <t>3233720215 3233720215</t>
-  </si>
-  <si>
-    <t>3233748012 3233748012</t>
-  </si>
-  <si>
-    <t>3233764569 3233764569</t>
-  </si>
-  <si>
-    <t>3233767105 3233767105</t>
-  </si>
-  <si>
-    <t>3233936659 3233936659</t>
-  </si>
-  <si>
-    <t>3233937870 3233937870</t>
-  </si>
-  <si>
-    <t>3233948161 3233948161</t>
-  </si>
-  <si>
-    <t>3233968150 3233968150</t>
-  </si>
-  <si>
-    <t>3234066541 3234066541</t>
-  </si>
-  <si>
-    <t>3234029844 3234029844</t>
-  </si>
-  <si>
-    <t>3234110194 3234110194</t>
+    <t>DIESEL DOUBLE FILTER</t>
+  </si>
+  <si>
+    <t>09:53</t>
+  </si>
+  <si>
+    <t>13:06</t>
+  </si>
+  <si>
+    <t>12:11</t>
+  </si>
+  <si>
+    <t>13:57</t>
+  </si>
+  <si>
+    <t>09:19</t>
+  </si>
+  <si>
+    <t>09:58</t>
+  </si>
+  <si>
+    <t>10:07</t>
+  </si>
+  <si>
+    <t>08:38</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>10:01</t>
+  </si>
+  <si>
+    <t>11:09</t>
+  </si>
+  <si>
+    <t>12:37</t>
+  </si>
+  <si>
+    <t>17:26</t>
+  </si>
+  <si>
+    <t>19:02</t>
+  </si>
+  <si>
+    <t>17:06</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>15:38</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА</t>
@@ -658,7 +601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -667,17 +610,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -717,319 +659,295 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46189</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F2">
-        <v>55.01</v>
-      </c>
-      <c r="G2" t="s">
-        <v>40</v>
+        <v>36.64</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.53</v>
       </c>
       <c r="H2">
-        <v>1.53</v>
+        <v>56.06</v>
       </c>
       <c r="I2" s="1">
-        <v>84.17</v>
+        <v>1.56</v>
       </c>
       <c r="J2">
-        <v>1.56</v>
-      </c>
-      <c r="K2" s="1">
-        <v>85.81999999999999</v>
-      </c>
-      <c r="L2" t="s">
-        <v>41</v>
+        <v>57.16</v>
+      </c>
+      <c r="K2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L2">
+        <v>61250</v>
       </c>
       <c r="M2">
-        <v>375195</v>
-      </c>
-      <c r="N2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>219723</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46189</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F3">
-        <v>36.64</v>
-      </c>
-      <c r="G3" t="s">
+        <v>55.01</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="H3">
+        <v>84.17</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="J3">
+        <v>85.81999999999999</v>
+      </c>
+      <c r="K3" t="s">
         <v>40</v>
       </c>
-      <c r="H3">
-        <v>1.53</v>
-      </c>
-      <c r="I3" s="1">
-        <v>56.06</v>
-      </c>
-      <c r="J3">
-        <v>1.56</v>
-      </c>
-      <c r="K3" s="1">
-        <v>57.16</v>
-      </c>
-      <c r="L3" t="s">
-        <v>42</v>
+      <c r="L3">
+        <v>375195</v>
       </c>
       <c r="M3">
-        <v>61250</v>
-      </c>
-      <c r="N3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>142658</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46191</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F4">
         <v>115</v>
       </c>
-      <c r="G4" t="s">
-        <v>40</v>
+      <c r="G4" s="1">
+        <v>1.55</v>
       </c>
       <c r="H4">
-        <v>1.55</v>
+        <v>178.25</v>
       </c>
       <c r="I4" s="1">
-        <v>178.25</v>
+        <v>1.58</v>
       </c>
       <c r="J4">
-        <v>1.58</v>
-      </c>
-      <c r="K4" s="1">
         <v>181.7</v>
       </c>
-      <c r="L4" t="s">
-        <v>43</v>
+      <c r="K4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L4">
+        <v>128922</v>
       </c>
       <c r="M4">
-        <v>128922</v>
-      </c>
-      <c r="N4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>220703</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
         <v>46191</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F5">
         <v>114.16</v>
       </c>
-      <c r="G5" t="s">
-        <v>40</v>
+      <c r="G5" s="1">
+        <v>1.55</v>
       </c>
       <c r="H5">
-        <v>1.55</v>
+        <v>176.95</v>
       </c>
       <c r="I5" s="1">
-        <v>176.95</v>
+        <v>1.58</v>
       </c>
       <c r="J5">
-        <v>1.58</v>
-      </c>
-      <c r="K5" s="1">
         <v>180.37</v>
       </c>
-      <c r="L5" t="s">
-        <v>44</v>
+      <c r="K5" t="s">
+        <v>42</v>
+      </c>
+      <c r="L5">
+        <v>132553</v>
       </c>
       <c r="M5">
-        <v>132553</v>
-      </c>
-      <c r="N5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>220773</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="3">
         <v>46195</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F6">
         <v>89.89</v>
       </c>
-      <c r="G6" t="s">
-        <v>40</v>
+      <c r="G6" s="1">
+        <v>1.49</v>
       </c>
       <c r="H6">
-        <v>1.49</v>
+        <v>133.94</v>
       </c>
       <c r="I6" s="1">
-        <v>133.94</v>
+        <v>1.52</v>
       </c>
       <c r="J6">
-        <v>1.52</v>
-      </c>
-      <c r="K6" s="1">
         <v>136.63</v>
       </c>
-      <c r="L6" t="s">
-        <v>45</v>
+      <c r="K6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L6">
+        <v>47040</v>
       </c>
       <c r="M6">
-        <v>246997</v>
-      </c>
-      <c r="N6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>222261</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="3">
         <v>46195</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s">
         <v>37</v>
       </c>
       <c r="F7">
-        <v>106.55</v>
-      </c>
-      <c r="G7" t="s">
-        <v>40</v>
+        <v>32.47</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.65</v>
       </c>
       <c r="H7">
-        <v>1.49</v>
+        <v>21.11</v>
       </c>
       <c r="I7" s="1">
-        <v>158.76</v>
+        <v>0.66</v>
       </c>
       <c r="J7">
-        <v>1.52</v>
-      </c>
-      <c r="K7" s="1">
-        <v>161.96</v>
-      </c>
-      <c r="L7" t="s">
-        <v>46</v>
+        <v>21.43</v>
+      </c>
+      <c r="K7" t="s">
+        <v>44</v>
+      </c>
+      <c r="L7">
+        <v>230921</v>
       </c>
       <c r="M7">
-        <v>129275</v>
-      </c>
-      <c r="N7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>222283</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="3">
         <v>46195</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F8">
-        <v>32.47</v>
-      </c>
-      <c r="G8" t="s">
-        <v>40</v>
+        <v>106.55</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1.49</v>
       </c>
       <c r="H8">
-        <v>0.65</v>
+        <v>158.76</v>
       </c>
       <c r="I8" s="1">
-        <v>21.11</v>
+        <v>1.52</v>
       </c>
       <c r="J8">
-        <v>0.66</v>
-      </c>
-      <c r="K8" s="1">
-        <v>21.43</v>
-      </c>
-      <c r="L8" t="s">
-        <v>47</v>
+        <v>161.96</v>
+      </c>
+      <c r="K8" t="s">
+        <v>45</v>
+      </c>
+      <c r="L8">
+        <v>129275</v>
       </c>
       <c r="M8">
-        <v>230921</v>
-      </c>
-      <c r="N8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <v>222292</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="3">
         <v>46196</v>
       </c>
@@ -1037,441 +955,411 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F9">
         <v>36.35</v>
       </c>
-      <c r="G9" t="s">
-        <v>40</v>
+      <c r="G9" s="1">
+        <v>1.48</v>
       </c>
       <c r="H9">
-        <v>1.48</v>
+        <v>53.8</v>
       </c>
       <c r="I9" s="1">
-        <v>53.8</v>
+        <v>1.51</v>
       </c>
       <c r="J9">
-        <v>1.51</v>
-      </c>
-      <c r="K9" s="1">
         <v>54.89</v>
       </c>
-      <c r="L9" t="s">
-        <v>48</v>
+      <c r="K9" t="s">
+        <v>46</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
       </c>
       <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>144767</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="3">
         <v>46196</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F10">
         <v>113.03</v>
       </c>
-      <c r="G10" t="s">
-        <v>40</v>
+      <c r="G10" s="1">
+        <v>1.49</v>
       </c>
       <c r="H10">
-        <v>1.49</v>
+        <v>168.41</v>
       </c>
       <c r="I10" s="1">
-        <v>168.41</v>
+        <v>1.52</v>
       </c>
       <c r="J10">
-        <v>1.52</v>
-      </c>
-      <c r="K10" s="1">
         <v>171.81</v>
       </c>
-      <c r="L10" t="s">
-        <v>49</v>
+      <c r="K10" t="s">
+        <v>47</v>
+      </c>
+      <c r="L10">
+        <v>132950</v>
       </c>
       <c r="M10">
-        <v>132950</v>
-      </c>
-      <c r="N10" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>222807</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="3">
         <v>46196</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F11">
         <v>43.95</v>
       </c>
-      <c r="G11" t="s">
-        <v>40</v>
+      <c r="G11" s="1">
+        <v>1.48</v>
       </c>
       <c r="H11">
-        <v>1.48</v>
+        <v>65.05</v>
       </c>
       <c r="I11" s="1">
-        <v>65.05</v>
+        <v>1.51</v>
       </c>
       <c r="J11">
-        <v>1.51</v>
-      </c>
-      <c r="K11" s="1">
         <v>66.36</v>
       </c>
-      <c r="L11" t="s">
-        <v>50</v>
+      <c r="K11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L11">
+        <v>74566</v>
       </c>
       <c r="M11">
-        <v>74566</v>
-      </c>
-      <c r="N11" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>222853</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="3">
         <v>46199</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F12">
         <v>33.61</v>
       </c>
-      <c r="G12" t="s">
-        <v>40</v>
+      <c r="G12" s="1">
+        <v>0.65</v>
       </c>
       <c r="H12">
-        <v>0.65</v>
+        <v>21.85</v>
       </c>
       <c r="I12" s="1">
-        <v>21.85</v>
+        <v>0.66</v>
       </c>
       <c r="J12">
-        <v>0.66</v>
-      </c>
-      <c r="K12" s="1">
         <v>22.18</v>
       </c>
-      <c r="L12" t="s">
-        <v>51</v>
+      <c r="K12" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12">
+        <v>231080</v>
       </c>
       <c r="M12">
-        <v>231080</v>
-      </c>
-      <c r="N12" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>224341</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="3">
         <v>46199</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F13">
         <v>103.6</v>
       </c>
-      <c r="G13" t="s">
-        <v>40</v>
+      <c r="G13" s="1">
+        <v>1.48</v>
       </c>
       <c r="H13">
-        <v>1.48</v>
+        <v>153.33</v>
       </c>
       <c r="I13" s="1">
-        <v>153.33</v>
+        <v>1.51</v>
       </c>
       <c r="J13">
-        <v>1.51</v>
-      </c>
-      <c r="K13" s="1">
         <v>156.44</v>
       </c>
-      <c r="L13" t="s">
-        <v>52</v>
+      <c r="K13" t="s">
+        <v>50</v>
+      </c>
+      <c r="L13">
+        <v>129611</v>
       </c>
       <c r="M13">
-        <v>129611</v>
-      </c>
-      <c r="N13" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+        <v>224412</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="3">
         <v>46199</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F14">
         <v>99.39</v>
       </c>
-      <c r="G14" t="s">
-        <v>40</v>
+      <c r="G14" s="1">
+        <v>1.77</v>
       </c>
       <c r="H14">
-        <v>1.74</v>
+        <v>175.92</v>
       </c>
       <c r="I14" s="1">
-        <v>172.94</v>
+        <v>1.77</v>
       </c>
       <c r="J14">
-        <v>1.77</v>
-      </c>
-      <c r="K14" s="1">
         <v>175.92</v>
       </c>
-      <c r="L14" t="s">
-        <v>53</v>
+      <c r="K14" t="s">
+        <v>51</v>
+      </c>
+      <c r="L14">
+        <v>133283</v>
       </c>
       <c r="M14">
-        <v>133283</v>
-      </c>
-      <c r="N14" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+        <v>224616</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="3">
         <v>46200</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F15">
         <v>97.47</v>
       </c>
-      <c r="G15" t="s">
-        <v>40</v>
+      <c r="G15" s="1">
+        <v>1.48</v>
       </c>
       <c r="H15">
-        <v>1.48</v>
+        <v>144.26</v>
       </c>
       <c r="I15" s="1">
-        <v>144.26</v>
+        <v>1.51</v>
       </c>
       <c r="J15">
-        <v>1.51</v>
-      </c>
-      <c r="K15" s="1">
         <v>147.18</v>
       </c>
-      <c r="L15" t="s">
-        <v>54</v>
+      <c r="K15" t="s">
+        <v>52</v>
+      </c>
+      <c r="L15">
+        <v>247458</v>
       </c>
       <c r="M15">
-        <v>247458</v>
-      </c>
-      <c r="N15" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+        <v>225014</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="3">
         <v>46202</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F16">
         <v>33.33</v>
       </c>
-      <c r="G16" t="s">
-        <v>40</v>
+      <c r="G16" s="1">
+        <v>1.47</v>
       </c>
       <c r="H16">
-        <v>1.47</v>
+        <v>49</v>
       </c>
       <c r="I16" s="1">
-        <v>49</v>
+        <v>1.5</v>
       </c>
       <c r="J16">
-        <v>1.5</v>
-      </c>
-      <c r="K16" s="1">
         <v>50</v>
       </c>
-      <c r="L16" t="s">
-        <v>55</v>
+      <c r="K16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L16">
+        <v>63150</v>
       </c>
       <c r="M16">
-        <v>63150</v>
-      </c>
-      <c r="N16" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+        <v>225625</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="3">
         <v>46203</v>
       </c>
       <c r="B17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" t="s">
         <v>15</v>
       </c>
-      <c r="C17" t="s">
-        <v>17</v>
-      </c>
       <c r="D17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F17">
         <v>36.46</v>
       </c>
-      <c r="G17" t="s">
-        <v>40</v>
+      <c r="G17" s="1">
+        <v>1.47</v>
       </c>
       <c r="H17">
-        <v>1.47</v>
+        <v>53.6</v>
       </c>
       <c r="I17" s="1">
-        <v>53.6</v>
+        <v>1.5</v>
       </c>
       <c r="J17">
-        <v>1.5</v>
-      </c>
-      <c r="K17" s="1">
         <v>54.69</v>
       </c>
-      <c r="L17" t="s">
-        <v>56</v>
+      <c r="K17" t="s">
+        <v>54</v>
+      </c>
+      <c r="L17">
+        <v>61770</v>
       </c>
       <c r="M17">
-        <v>61770</v>
-      </c>
-      <c r="N17" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+        <v>226134</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="3">
         <v>46203</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D18" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" t="s">
         <v>35</v>
-      </c>
-      <c r="E18" t="s">
-        <v>36</v>
       </c>
       <c r="F18">
         <v>35.07</v>
       </c>
-      <c r="G18" t="s">
-        <v>40</v>
+      <c r="G18" s="1">
+        <v>1.47</v>
       </c>
       <c r="H18">
-        <v>1.47</v>
+        <v>51.55</v>
       </c>
       <c r="I18" s="1">
-        <v>51.55</v>
+        <v>1.5</v>
       </c>
       <c r="J18">
-        <v>1.5</v>
-      </c>
-      <c r="K18" s="1">
         <v>52.6</v>
       </c>
-      <c r="L18" t="s">
-        <v>57</v>
+      <c r="K18" t="s">
+        <v>55</v>
+      </c>
+      <c r="L18">
+        <v>62052</v>
       </c>
       <c r="M18">
-        <v>62052</v>
-      </c>
-      <c r="N18" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+        <v>226143</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="4" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -1479,29 +1367,29 @@
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:13">
       <c r="A22" s="5" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B23" s="7">
         <v>739.7</v>
@@ -1519,9 +1407,9 @@
         <v>1136.09</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:13">
       <c r="A24" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B24" s="7">
         <v>276.81</v>
@@ -1539,9 +1427,9 @@
         <v>421.52</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:13">
       <c r="A25" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B25" s="7">
         <v>99.39</v>
@@ -1550,18 +1438,18 @@
         <v>1</v>
       </c>
       <c r="D25" s="8">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="E25" s="7">
-        <v>172.94</v>
+        <v>175.92</v>
       </c>
       <c r="F25" s="7">
         <v>175.92</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:13">
       <c r="A26" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" s="7">
         <v>66.08</v>
@@ -1579,9 +1467,9 @@
         <v>43.61</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:13">
       <c r="A27" s="9" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="B27" s="10">
         <v>1181.98</v>
@@ -1591,7 +1479,7 @@
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="10">
-        <v>1743.03</v>
+        <v>1746.01</v>
       </c>
       <c r="F27" s="10">
         <v>1777.14</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА.xlsx
@@ -254,7 +254,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -1542,7 +1542,7 @@
         <v>12</v>
       </c>
       <c r="D24" s="8">
-        <v>1.6853</v>
+        <v>1.685341</v>
       </c>
       <c r="E24" s="7">
         <v>1808</v>
@@ -1562,7 +1562,7 @@
         <v>4</v>
       </c>
       <c r="D25" s="8">
-        <v>1.5061</v>
+        <v>1.506092</v>
       </c>
       <c r="E25" s="7">
         <v>224.98</v>
@@ -1582,7 +1582,7 @@
         <v>2</v>
       </c>
       <c r="D26" s="8">
-        <v>0.63</v>
+        <v>0.630043</v>
       </c>
       <c r="E26" s="7">
         <v>30.45</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="78">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -646,7 +649,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -659,13 +662,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -708,802 +711,859 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F2">
         <v>28.46</v>
       </c>
       <c r="G2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H2">
+        <v>1.369</v>
+      </c>
+      <c r="I2" s="1">
         <v>1.47</v>
       </c>
-      <c r="I2" s="1">
-        <v>41.84</v>
-      </c>
       <c r="J2">
+        <v>41.8362</v>
+      </c>
+      <c r="K2" s="1">
         <v>1.5</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>42.69</v>
       </c>
-      <c r="L2" t="s">
-        <v>36</v>
-      </c>
-      <c r="M2">
+      <c r="M2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N2">
         <v>75526</v>
       </c>
-      <c r="N2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="3">
         <v>46220</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F3">
-        <v>80.03</v>
+        <v>80.03100000000001</v>
       </c>
       <c r="G3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H3">
+        <v>1.499</v>
+      </c>
+      <c r="I3" s="1">
         <v>1.6</v>
       </c>
-      <c r="I3" s="1">
-        <v>128.05</v>
-      </c>
       <c r="J3">
+        <v>128.0496</v>
+      </c>
+      <c r="K3" s="1">
         <v>1.63</v>
       </c>
-      <c r="K3" s="1">
-        <v>130.45</v>
-      </c>
-      <c r="L3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M3">
+      <c r="L3" s="1">
+        <v>130.45053</v>
+      </c>
+      <c r="M3" t="s">
+        <v>38</v>
+      </c>
+      <c r="N3">
         <v>147070</v>
       </c>
-      <c r="N3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="3">
         <v>46222</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F4">
-        <v>114.38</v>
+        <v>114.381</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H4">
+        <v>1.528</v>
+      </c>
+      <c r="I4" s="1">
         <v>1.65</v>
       </c>
-      <c r="I4" s="1">
-        <v>188.73</v>
-      </c>
       <c r="J4">
+        <v>188.72865</v>
+      </c>
+      <c r="K4" s="1">
         <v>1.68</v>
       </c>
-      <c r="K4" s="1">
-        <v>192.16</v>
-      </c>
-      <c r="L4" t="s">
-        <v>38</v>
-      </c>
-      <c r="M4">
+      <c r="L4" s="1">
+        <v>192.16008</v>
+      </c>
+      <c r="M4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N4">
         <v>131535</v>
       </c>
-      <c r="N4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="3">
         <v>46222</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F5">
-        <v>88.93000000000001</v>
+        <v>88.929</v>
       </c>
       <c r="G5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H5">
+        <v>1.528</v>
+      </c>
+      <c r="I5" s="1">
         <v>1.65</v>
       </c>
-      <c r="I5" s="1">
-        <v>146.73</v>
-      </c>
       <c r="J5">
+        <v>146.73285</v>
+      </c>
+      <c r="K5" s="1">
         <v>1.68</v>
       </c>
-      <c r="K5" s="1">
-        <v>149.4</v>
-      </c>
-      <c r="L5" t="s">
-        <v>39</v>
-      </c>
-      <c r="M5">
+      <c r="L5" s="1">
+        <v>149.40072</v>
+      </c>
+      <c r="M5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N5">
         <v>147340</v>
       </c>
-      <c r="N5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="3">
         <v>46224</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6">
         <v>32.98</v>
       </c>
       <c r="G6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H6">
+        <v>1.389</v>
+      </c>
+      <c r="I6" s="1">
         <v>1.5</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>49.47</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>1.53</v>
       </c>
-      <c r="K6" s="1">
-        <v>50.46</v>
-      </c>
-      <c r="L6" t="s">
-        <v>40</v>
-      </c>
-      <c r="M6">
+      <c r="L6" s="1">
+        <v>50.4594</v>
+      </c>
+      <c r="M6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N6">
         <v>62448</v>
       </c>
-      <c r="N6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="3">
         <v>46224</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7">
-        <v>104.14</v>
+        <v>104.143</v>
       </c>
       <c r="G7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H7">
+        <v>1.564</v>
+      </c>
+      <c r="I7" s="1">
         <v>1.65</v>
       </c>
-      <c r="I7" s="1">
-        <v>171.83</v>
-      </c>
       <c r="J7">
+        <v>171.83595</v>
+      </c>
+      <c r="K7" s="1">
         <v>1.68</v>
       </c>
-      <c r="K7" s="1">
-        <v>174.96</v>
-      </c>
-      <c r="L7" t="s">
-        <v>41</v>
-      </c>
-      <c r="M7">
+      <c r="L7" s="1">
+        <v>174.96024</v>
+      </c>
+      <c r="M7" t="s">
+        <v>42</v>
+      </c>
+      <c r="N7">
         <v>248405</v>
       </c>
-      <c r="N7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="3">
         <v>46225</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8">
-        <v>19.77</v>
+        <v>19.766</v>
       </c>
       <c r="G8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1">
         <v>0.63</v>
       </c>
-      <c r="I8" s="1">
-        <v>12.46</v>
-      </c>
       <c r="J8">
+        <v>12.45258</v>
+      </c>
+      <c r="K8" s="1">
         <v>0.64</v>
       </c>
-      <c r="K8" s="1">
-        <v>12.65</v>
-      </c>
-      <c r="L8" t="s">
-        <v>42</v>
-      </c>
-      <c r="M8">
+      <c r="L8" s="1">
+        <v>12.65024</v>
+      </c>
+      <c r="M8" t="s">
+        <v>43</v>
+      </c>
+      <c r="N8">
         <v>231486</v>
       </c>
-      <c r="N8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="3">
         <v>46226</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F9">
-        <v>87.61</v>
+        <v>87.61199999999999</v>
       </c>
       <c r="G9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H9">
+        <v>1.588</v>
+      </c>
+      <c r="I9" s="1">
         <v>1.67</v>
       </c>
-      <c r="I9" s="1">
-        <v>146.31</v>
-      </c>
       <c r="J9">
+        <v>146.31204</v>
+      </c>
+      <c r="K9" s="1">
         <v>1.7</v>
       </c>
-      <c r="K9" s="1">
-        <v>148.94</v>
-      </c>
-      <c r="L9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M9">
+      <c r="L9" s="1">
+        <v>148.9404</v>
+      </c>
+      <c r="M9" t="s">
+        <v>44</v>
+      </c>
+      <c r="N9">
         <v>147585</v>
       </c>
-      <c r="N9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="3">
         <v>46227</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F10">
         <v>116</v>
       </c>
       <c r="G10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H10">
+        <v>1.619</v>
+      </c>
+      <c r="I10" s="1">
         <v>1.69</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10">
         <v>196.04</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="1">
         <v>1.72</v>
       </c>
-      <c r="K10" s="1">
+      <c r="L10" s="1">
         <v>199.52</v>
       </c>
-      <c r="L10" t="s">
-        <v>44</v>
-      </c>
-      <c r="M10">
+      <c r="M10" t="s">
+        <v>45</v>
+      </c>
+      <c r="N10">
         <v>131925</v>
       </c>
-      <c r="N10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="3">
         <v>46227</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F11">
         <v>78.36</v>
       </c>
       <c r="G11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H11">
+        <v>1.619</v>
+      </c>
+      <c r="I11" s="1">
         <v>1.69</v>
       </c>
-      <c r="I11" s="1">
-        <v>132.43</v>
-      </c>
       <c r="J11">
+        <v>132.4284</v>
+      </c>
+      <c r="K11" s="1">
         <v>1.72</v>
       </c>
-      <c r="K11" s="1">
-        <v>134.78</v>
-      </c>
-      <c r="L11" t="s">
-        <v>45</v>
-      </c>
-      <c r="M11">
+      <c r="L11" s="1">
+        <v>134.7792</v>
+      </c>
+      <c r="M11" t="s">
+        <v>46</v>
+      </c>
+      <c r="N11">
         <v>134999</v>
       </c>
-      <c r="N11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="3">
         <v>46227</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F12">
         <v>40</v>
       </c>
       <c r="G12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H12">
+        <v>1.619</v>
+      </c>
+      <c r="I12" s="1">
         <v>1.69</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12">
         <v>67.59999999999999</v>
       </c>
-      <c r="J12">
+      <c r="K12" s="1">
         <v>1.72</v>
       </c>
-      <c r="K12" s="1">
+      <c r="L12" s="1">
         <v>68.8</v>
       </c>
-      <c r="L12" t="s">
-        <v>46</v>
-      </c>
-      <c r="M12">
+      <c r="M12" t="s">
+        <v>47</v>
+      </c>
+      <c r="N12">
         <v>147757</v>
       </c>
-      <c r="N12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="3">
         <v>46232</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F13">
-        <v>96.19</v>
+        <v>96.18899999999999</v>
       </c>
       <c r="G13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H13">
+        <v>1.674</v>
+      </c>
+      <c r="I13" s="1">
         <v>1.72</v>
       </c>
-      <c r="I13" s="1">
-        <v>165.45</v>
-      </c>
       <c r="J13">
+        <v>165.44508</v>
+      </c>
+      <c r="K13" s="1">
         <v>1.75</v>
       </c>
-      <c r="K13" s="1">
-        <v>168.33</v>
-      </c>
-      <c r="L13" t="s">
-        <v>47</v>
-      </c>
-      <c r="M13">
+      <c r="L13" s="1">
+        <v>168.33075</v>
+      </c>
+      <c r="M13" t="s">
+        <v>48</v>
+      </c>
+      <c r="N13">
         <v>148045</v>
       </c>
-      <c r="N13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="O13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="3">
         <v>46232</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F14">
         <v>43.71</v>
       </c>
       <c r="G14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H14">
+        <v>1.449</v>
+      </c>
+      <c r="I14" s="1">
         <v>1.52</v>
       </c>
-      <c r="I14" s="1">
-        <v>66.44</v>
-      </c>
       <c r="J14">
+        <v>66.4392</v>
+      </c>
+      <c r="K14" s="1">
         <v>1.55</v>
       </c>
-      <c r="K14" s="1">
-        <v>67.75</v>
-      </c>
-      <c r="L14" t="s">
-        <v>48</v>
-      </c>
-      <c r="M14">
+      <c r="L14" s="1">
+        <v>67.7505</v>
+      </c>
+      <c r="M14" t="s">
+        <v>49</v>
+      </c>
+      <c r="N14">
         <v>76180</v>
       </c>
-      <c r="N14" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="O14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="3">
         <v>46233</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F15">
-        <v>28.56</v>
+        <v>28.563</v>
       </c>
       <c r="G15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15" s="1">
         <v>0.63</v>
       </c>
-      <c r="I15" s="1">
-        <v>17.99</v>
-      </c>
       <c r="J15">
+        <v>17.99469</v>
+      </c>
+      <c r="K15" s="1">
         <v>0.64</v>
       </c>
-      <c r="K15" s="1">
-        <v>18.28</v>
-      </c>
-      <c r="L15" t="s">
-        <v>49</v>
-      </c>
-      <c r="M15">
+      <c r="L15" s="1">
+        <v>18.28032</v>
+      </c>
+      <c r="M15" t="s">
+        <v>50</v>
+      </c>
+      <c r="N15">
         <v>231609</v>
       </c>
-      <c r="N15" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="O15" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" s="3">
         <v>46234</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F16">
-        <v>115.36</v>
+        <v>115.362</v>
       </c>
       <c r="G16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H16">
+        <v>1.689</v>
+      </c>
+      <c r="I16" s="1">
         <v>1.74</v>
       </c>
-      <c r="I16" s="1">
-        <v>200.73</v>
-      </c>
       <c r="J16">
+        <v>200.72988</v>
+      </c>
+      <c r="K16" s="1">
         <v>1.77</v>
       </c>
-      <c r="K16" s="1">
-        <v>204.19</v>
-      </c>
-      <c r="L16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M16">
+      <c r="L16" s="1">
+        <v>204.19074</v>
+      </c>
+      <c r="M16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16">
         <v>135370</v>
       </c>
-      <c r="N16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="O16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" s="3">
         <v>46234</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F17">
-        <v>44.23</v>
+        <v>44.232</v>
       </c>
       <c r="G17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H17">
+        <v>1.459</v>
+      </c>
+      <c r="I17" s="1">
         <v>1.52</v>
       </c>
-      <c r="I17" s="1">
-        <v>67.23</v>
-      </c>
       <c r="J17">
+        <v>67.23264</v>
+      </c>
+      <c r="K17" s="1">
         <v>1.55</v>
       </c>
-      <c r="K17" s="1">
-        <v>68.56</v>
-      </c>
-      <c r="L17" t="s">
-        <v>42</v>
-      </c>
-      <c r="M17">
+      <c r="L17" s="1">
+        <v>68.5596</v>
+      </c>
+      <c r="M17" t="s">
+        <v>43</v>
+      </c>
+      <c r="N17">
         <v>175850</v>
       </c>
-      <c r="N17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="O17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" s="3">
         <v>46234</v>
       </c>
       <c r="B18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F18">
         <v>86.78</v>
       </c>
       <c r="G18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H18">
+        <v>1.689</v>
+      </c>
+      <c r="I18" s="1">
         <v>1.74</v>
       </c>
-      <c r="I18" s="1">
-        <v>151</v>
-      </c>
       <c r="J18">
+        <v>150.9972</v>
+      </c>
+      <c r="K18" s="1">
         <v>1.77</v>
       </c>
-      <c r="K18" s="1">
-        <v>153.6</v>
-      </c>
-      <c r="L18" t="s">
-        <v>51</v>
-      </c>
-      <c r="M18">
+      <c r="L18" s="1">
+        <v>153.6006</v>
+      </c>
+      <c r="M18" t="s">
+        <v>52</v>
+      </c>
+      <c r="N18">
         <v>132217</v>
       </c>
-      <c r="N18" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="O18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" s="3">
         <v>46234</v>
       </c>
       <c r="B19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F19">
         <v>65</v>
       </c>
       <c r="G19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H19">
+        <v>1.689</v>
+      </c>
+      <c r="I19" s="1">
         <v>1.74</v>
       </c>
-      <c r="I19" s="1">
+      <c r="J19">
         <v>113.1</v>
       </c>
-      <c r="J19">
+      <c r="K19" s="1">
         <v>1.77</v>
       </c>
-      <c r="K19" s="1">
+      <c r="L19" s="1">
         <v>115.05</v>
       </c>
-      <c r="L19" t="s">
-        <v>52</v>
-      </c>
-      <c r="M19">
+      <c r="M19" t="s">
+        <v>53</v>
+      </c>
+      <c r="N19">
         <v>148264</v>
       </c>
-      <c r="N19" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="O19" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -1511,38 +1571,38 @@
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:15">
       <c r="A23" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24" s="7">
-        <v>1072.78</v>
+        <v>1072.787</v>
       </c>
       <c r="C24" s="7">
         <v>12</v>
       </c>
       <c r="D24" s="8">
-        <v>1.685341</v>
+        <v>1.68533</v>
       </c>
       <c r="E24" s="7">
         <v>1808</v>
@@ -1551,18 +1611,18 @@
         <v>1840.18</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:15">
       <c r="A25" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B25" s="7">
-        <v>149.38</v>
+        <v>149.382</v>
       </c>
       <c r="C25" s="7">
         <v>4</v>
       </c>
       <c r="D25" s="8">
-        <v>1.506092</v>
+        <v>1.506059</v>
       </c>
       <c r="E25" s="7">
         <v>224.98</v>
@@ -1571,18 +1631,18 @@
         <v>229.46</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:15">
       <c r="A26" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B26" s="7">
-        <v>48.33</v>
+        <v>48.329</v>
       </c>
       <c r="C26" s="7">
         <v>2</v>
       </c>
       <c r="D26" s="8">
-        <v>0.630043</v>
+        <v>0.63</v>
       </c>
       <c r="E26" s="7">
         <v>30.45</v>
@@ -1591,12 +1651,12 @@
         <v>30.93</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:15">
       <c r="A27" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B27" s="10">
-        <v>1270.49</v>
+        <v>1270.498</v>
       </c>
       <c r="C27" s="10">
         <v>18</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="77">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -255,9 +252,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -351,10 +348,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -649,7 +646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -662,13 +659,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -711,859 +708,802 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F2">
         <v>28.46</v>
       </c>
       <c r="G2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2">
+        <v>1.47</v>
+      </c>
+      <c r="I2" s="1">
+        <v>41.836</v>
+      </c>
+      <c r="J2">
+        <v>1.5</v>
+      </c>
+      <c r="K2" s="1">
+        <v>42.69</v>
+      </c>
+      <c r="L2" t="s">
         <v>36</v>
       </c>
-      <c r="H2">
-        <v>1.369</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.47</v>
-      </c>
-      <c r="J2">
-        <v>41.8362</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L2" s="1">
-        <v>42.69</v>
-      </c>
-      <c r="M2" t="s">
-        <v>37</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>75526</v>
       </c>
-      <c r="O2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46220</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F3">
         <v>80.03100000000001</v>
       </c>
       <c r="G3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H3">
-        <v>1.499</v>
+        <v>1.6</v>
       </c>
       <c r="I3" s="1">
-        <v>1.6</v>
+        <v>128.05</v>
       </c>
       <c r="J3">
-        <v>128.0496</v>
+        <v>1.63</v>
       </c>
       <c r="K3" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L3" s="1">
-        <v>130.45053</v>
-      </c>
-      <c r="M3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N3">
+        <v>130.451</v>
+      </c>
+      <c r="L3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3">
         <v>147070</v>
       </c>
-      <c r="O3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46222</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F4">
         <v>114.381</v>
       </c>
       <c r="G4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H4">
-        <v>1.528</v>
+        <v>1.65</v>
       </c>
       <c r="I4" s="1">
-        <v>1.65</v>
+        <v>188.729</v>
       </c>
       <c r="J4">
-        <v>188.72865</v>
+        <v>1.68</v>
       </c>
       <c r="K4" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L4" s="1">
-        <v>192.16008</v>
-      </c>
-      <c r="M4" t="s">
-        <v>39</v>
-      </c>
-      <c r="N4">
+        <v>192.16</v>
+      </c>
+      <c r="L4" t="s">
+        <v>38</v>
+      </c>
+      <c r="M4">
         <v>131535</v>
       </c>
-      <c r="O4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46222</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F5">
         <v>88.929</v>
       </c>
       <c r="G5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H5">
-        <v>1.528</v>
+        <v>1.65</v>
       </c>
       <c r="I5" s="1">
-        <v>1.65</v>
+        <v>146.733</v>
       </c>
       <c r="J5">
-        <v>146.73285</v>
+        <v>1.68</v>
       </c>
       <c r="K5" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L5" s="1">
-        <v>149.40072</v>
-      </c>
-      <c r="M5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N5">
+        <v>149.401</v>
+      </c>
+      <c r="L5" t="s">
+        <v>39</v>
+      </c>
+      <c r="M5">
         <v>147340</v>
       </c>
-      <c r="O5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
         <v>46224</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F6">
         <v>32.98</v>
       </c>
       <c r="G6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H6">
-        <v>1.389</v>
+        <v>1.5</v>
       </c>
       <c r="I6" s="1">
-        <v>1.5</v>
+        <v>49.47</v>
       </c>
       <c r="J6">
-        <v>49.47</v>
+        <v>1.53</v>
       </c>
       <c r="K6" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="L6" s="1">
-        <v>50.4594</v>
-      </c>
-      <c r="M6" t="s">
-        <v>41</v>
-      </c>
-      <c r="N6">
+        <v>50.459</v>
+      </c>
+      <c r="L6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M6">
         <v>62448</v>
       </c>
-      <c r="O6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="N6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
         <v>46224</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F7">
         <v>104.143</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H7">
-        <v>1.564</v>
+        <v>1.65</v>
       </c>
       <c r="I7" s="1">
-        <v>1.65</v>
+        <v>171.836</v>
       </c>
       <c r="J7">
-        <v>171.83595</v>
+        <v>1.68</v>
       </c>
       <c r="K7" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L7" s="1">
-        <v>174.96024</v>
-      </c>
-      <c r="M7" t="s">
-        <v>42</v>
-      </c>
-      <c r="N7">
+        <v>174.96</v>
+      </c>
+      <c r="L7" t="s">
+        <v>41</v>
+      </c>
+      <c r="M7">
         <v>248405</v>
       </c>
-      <c r="O7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="N7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="3">
         <v>46225</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F8">
         <v>19.766</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I8" s="1">
-        <v>0.63</v>
+        <v>12.453</v>
       </c>
       <c r="J8">
-        <v>12.45258</v>
+        <v>0.64</v>
       </c>
       <c r="K8" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L8" s="1">
-        <v>12.65024</v>
-      </c>
-      <c r="M8" t="s">
-        <v>43</v>
-      </c>
-      <c r="N8">
+        <v>12.65</v>
+      </c>
+      <c r="L8" t="s">
+        <v>42</v>
+      </c>
+      <c r="M8">
         <v>231486</v>
       </c>
-      <c r="O8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="N8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="3">
         <v>46226</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F9">
         <v>87.61199999999999</v>
       </c>
       <c r="G9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H9">
-        <v>1.588</v>
+        <v>1.67</v>
       </c>
       <c r="I9" s="1">
-        <v>1.67</v>
+        <v>146.312</v>
       </c>
       <c r="J9">
-        <v>146.31204</v>
+        <v>1.7</v>
       </c>
       <c r="K9" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L9" s="1">
-        <v>148.9404</v>
-      </c>
-      <c r="M9" t="s">
-        <v>44</v>
-      </c>
-      <c r="N9">
+        <v>148.94</v>
+      </c>
+      <c r="L9" t="s">
+        <v>43</v>
+      </c>
+      <c r="M9">
         <v>147585</v>
       </c>
-      <c r="O9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="N9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="3">
         <v>46227</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F10">
         <v>116</v>
       </c>
       <c r="G10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H10">
-        <v>1.619</v>
+        <v>1.69</v>
       </c>
       <c r="I10" s="1">
-        <v>1.69</v>
+        <v>196.04</v>
       </c>
       <c r="J10">
-        <v>196.04</v>
+        <v>1.72</v>
       </c>
       <c r="K10" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L10" s="1">
         <v>199.52</v>
       </c>
-      <c r="M10" t="s">
-        <v>45</v>
-      </c>
-      <c r="N10">
+      <c r="L10" t="s">
+        <v>44</v>
+      </c>
+      <c r="M10">
         <v>131925</v>
       </c>
-      <c r="O10" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="N10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="3">
         <v>46227</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F11">
         <v>78.36</v>
       </c>
       <c r="G11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H11">
-        <v>1.619</v>
+        <v>1.69</v>
       </c>
       <c r="I11" s="1">
-        <v>1.69</v>
+        <v>132.428</v>
       </c>
       <c r="J11">
-        <v>132.4284</v>
+        <v>1.72</v>
       </c>
       <c r="K11" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L11" s="1">
-        <v>134.7792</v>
-      </c>
-      <c r="M11" t="s">
-        <v>46</v>
-      </c>
-      <c r="N11">
+        <v>134.779</v>
+      </c>
+      <c r="L11" t="s">
+        <v>45</v>
+      </c>
+      <c r="M11">
         <v>134999</v>
       </c>
-      <c r="O11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="N11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="3">
         <v>46227</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F12">
         <v>40</v>
       </c>
       <c r="G12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H12">
-        <v>1.619</v>
+        <v>1.69</v>
       </c>
       <c r="I12" s="1">
-        <v>1.69</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="J12">
-        <v>67.59999999999999</v>
+        <v>1.72</v>
       </c>
       <c r="K12" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L12" s="1">
         <v>68.8</v>
       </c>
-      <c r="M12" t="s">
-        <v>47</v>
-      </c>
-      <c r="N12">
+      <c r="L12" t="s">
+        <v>46</v>
+      </c>
+      <c r="M12">
         <v>147757</v>
       </c>
-      <c r="O12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+      <c r="N12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="3">
         <v>46232</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F13">
         <v>96.18899999999999</v>
       </c>
       <c r="G13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H13">
-        <v>1.674</v>
+        <v>1.72</v>
       </c>
       <c r="I13" s="1">
-        <v>1.72</v>
+        <v>165.445</v>
       </c>
       <c r="J13">
-        <v>165.44508</v>
+        <v>1.75</v>
       </c>
       <c r="K13" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L13" s="1">
-        <v>168.33075</v>
-      </c>
-      <c r="M13" t="s">
-        <v>48</v>
-      </c>
-      <c r="N13">
+        <v>168.331</v>
+      </c>
+      <c r="L13" t="s">
+        <v>47</v>
+      </c>
+      <c r="M13">
         <v>148045</v>
       </c>
-      <c r="O13" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+      <c r="N13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="3">
         <v>46232</v>
       </c>
       <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
         <v>16</v>
       </c>
-      <c r="C14" t="s">
-        <v>17</v>
-      </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F14">
         <v>43.71</v>
       </c>
       <c r="G14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H14">
-        <v>1.449</v>
+        <v>1.52</v>
       </c>
       <c r="I14" s="1">
-        <v>1.52</v>
+        <v>66.43899999999999</v>
       </c>
       <c r="J14">
-        <v>66.4392</v>
+        <v>1.55</v>
       </c>
       <c r="K14" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L14" s="1">
-        <v>67.7505</v>
-      </c>
-      <c r="M14" t="s">
-        <v>49</v>
-      </c>
-      <c r="N14">
+        <v>67.75</v>
+      </c>
+      <c r="L14" t="s">
+        <v>48</v>
+      </c>
+      <c r="M14">
         <v>76180</v>
       </c>
-      <c r="O14" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+      <c r="N14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="3">
         <v>46233</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F15">
         <v>28.563</v>
       </c>
       <c r="G15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I15" s="1">
-        <v>0.63</v>
+        <v>17.995</v>
       </c>
       <c r="J15">
-        <v>17.99469</v>
+        <v>0.64</v>
       </c>
       <c r="K15" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L15" s="1">
-        <v>18.28032</v>
-      </c>
-      <c r="M15" t="s">
-        <v>50</v>
-      </c>
-      <c r="N15">
+        <v>18.28</v>
+      </c>
+      <c r="L15" t="s">
+        <v>49</v>
+      </c>
+      <c r="M15">
         <v>231609</v>
       </c>
-      <c r="O15" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+      <c r="N15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="3">
         <v>46234</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F16">
         <v>115.362</v>
       </c>
       <c r="G16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H16">
-        <v>1.689</v>
+        <v>1.74</v>
       </c>
       <c r="I16" s="1">
-        <v>1.74</v>
+        <v>200.73</v>
       </c>
       <c r="J16">
-        <v>200.72988</v>
+        <v>1.77</v>
       </c>
       <c r="K16" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L16" s="1">
-        <v>204.19074</v>
-      </c>
-      <c r="M16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N16">
+        <v>204.191</v>
+      </c>
+      <c r="L16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16">
         <v>135370</v>
       </c>
-      <c r="O16" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+      <c r="N16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="3">
         <v>46234</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D17" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" t="s">
         <v>32</v>
-      </c>
-      <c r="E17" t="s">
-        <v>33</v>
       </c>
       <c r="F17">
         <v>44.232</v>
       </c>
       <c r="G17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H17">
-        <v>1.459</v>
+        <v>1.52</v>
       </c>
       <c r="I17" s="1">
-        <v>1.52</v>
+        <v>67.233</v>
       </c>
       <c r="J17">
-        <v>67.23264</v>
+        <v>1.55</v>
       </c>
       <c r="K17" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L17" s="1">
-        <v>68.5596</v>
-      </c>
-      <c r="M17" t="s">
-        <v>43</v>
-      </c>
-      <c r="N17">
+        <v>68.56</v>
+      </c>
+      <c r="L17" t="s">
+        <v>42</v>
+      </c>
+      <c r="M17">
         <v>175850</v>
       </c>
-      <c r="O17" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+      <c r="N17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="3">
         <v>46234</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F18">
         <v>86.78</v>
       </c>
       <c r="G18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H18">
-        <v>1.689</v>
+        <v>1.74</v>
       </c>
       <c r="I18" s="1">
-        <v>1.74</v>
+        <v>150.997</v>
       </c>
       <c r="J18">
-        <v>150.9972</v>
+        <v>1.77</v>
       </c>
       <c r="K18" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L18" s="1">
-        <v>153.6006</v>
-      </c>
-      <c r="M18" t="s">
-        <v>52</v>
-      </c>
-      <c r="N18">
+        <v>153.601</v>
+      </c>
+      <c r="L18" t="s">
+        <v>51</v>
+      </c>
+      <c r="M18">
         <v>132217</v>
       </c>
-      <c r="O18" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
+      <c r="N18" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="3">
         <v>46234</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F19">
         <v>65</v>
       </c>
       <c r="G19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H19">
-        <v>1.689</v>
+        <v>1.74</v>
       </c>
       <c r="I19" s="1">
-        <v>1.74</v>
+        <v>113.1</v>
       </c>
       <c r="J19">
-        <v>113.1</v>
+        <v>1.77</v>
       </c>
       <c r="K19" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L19" s="1">
         <v>115.05</v>
       </c>
-      <c r="M19" t="s">
-        <v>53</v>
-      </c>
-      <c r="N19">
+      <c r="L19" t="s">
+        <v>52</v>
+      </c>
+      <c r="M19">
         <v>148264</v>
       </c>
-      <c r="O19" t="s">
+      <c r="N19" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="4" t="s">
         <v>71</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
-      <c r="A22" s="4" t="s">
-        <v>72</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -1571,89 +1511,89 @@
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:14">
       <c r="A23" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="C23" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="D23" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>76</v>
-      </c>
       <c r="E23" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B24" s="7">
         <v>1072.787</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="8">
         <v>12</v>
       </c>
       <c r="D24" s="8">
-        <v>1.68533</v>
-      </c>
-      <c r="E24" s="7">
+        <v>1.685</v>
+      </c>
+      <c r="E24" s="8">
         <v>1808</v>
       </c>
-      <c r="F24" s="7">
-        <v>1840.18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
+      <c r="F24" s="8">
+        <v>1840.184</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" s="7">
         <v>149.382</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="8">
         <v>4</v>
       </c>
       <c r="D25" s="8">
-        <v>1.506059</v>
-      </c>
-      <c r="E25" s="7">
-        <v>224.98</v>
-      </c>
-      <c r="F25" s="7">
-        <v>229.46</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
+        <v>1.506</v>
+      </c>
+      <c r="E25" s="8">
+        <v>224.978</v>
+      </c>
+      <c r="F25" s="8">
+        <v>229.459</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="7">
         <v>48.329</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="8">
         <v>2</v>
       </c>
       <c r="D26" s="8">
         <v>0.63</v>
       </c>
-      <c r="E26" s="7">
-        <v>30.45</v>
-      </c>
-      <c r="F26" s="7">
+      <c r="E26" s="8">
+        <v>30.448</v>
+      </c>
+      <c r="F26" s="8">
         <v>30.93</v>
       </c>
     </row>
-    <row r="27" spans="1:15">
+    <row r="27" spans="1:14">
       <c r="A27" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B27" s="10">
         <v>1270.498</v>
@@ -1663,10 +1603,10 @@
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="10">
-        <v>2063.43</v>
+        <v>2063.426</v>
       </c>
       <c r="F27" s="10">
-        <v>2100.57</v>
+        <v>2100.573</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА/ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА.xlsx
@@ -705,10 +705,10 @@
         <v>36</v>
       </c>
       <c r="H2" s="1">
-        <v>1.409</v>
+        <v>1.53</v>
       </c>
       <c r="I2" s="1">
-        <v>49.315</v>
+        <v>53.55</v>
       </c>
       <c r="J2" s="1">
         <v>1.56</v>
@@ -749,10 +749,10 @@
         <v>36</v>
       </c>
       <c r="H3" s="1">
-        <v>1.429</v>
+        <v>1.53</v>
       </c>
       <c r="I3" s="1">
-        <v>60.747</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="J3" s="1">
         <v>1.56</v>
@@ -793,10 +793,10 @@
         <v>36</v>
       </c>
       <c r="H4" s="1">
-        <v>1.429</v>
+        <v>1.54</v>
       </c>
       <c r="I4" s="1">
-        <v>28.58</v>
+        <v>30.8</v>
       </c>
       <c r="J4" s="1">
         <v>1.57</v>
@@ -837,10 +837,10 @@
         <v>36</v>
       </c>
       <c r="H5" s="1">
-        <v>1.429</v>
+        <v>1.54</v>
       </c>
       <c r="I5" s="1">
-        <v>53.016</v>
+        <v>57.134</v>
       </c>
       <c r="J5" s="1">
         <v>1.57</v>
@@ -881,10 +881,10 @@
         <v>36</v>
       </c>
       <c r="H6" s="1">
-        <v>1.689</v>
+        <v>1.81</v>
       </c>
       <c r="I6" s="1">
-        <v>190.908</v>
+        <v>204.584</v>
       </c>
       <c r="J6" s="1">
         <v>1.84</v>
@@ -925,10 +925,10 @@
         <v>36</v>
       </c>
       <c r="H7" s="1">
-        <v>1.708</v>
+        <v>1.82</v>
       </c>
       <c r="I7" s="1">
-        <v>198.76</v>
+        <v>211.793</v>
       </c>
       <c r="J7" s="1">
         <v>1.85</v>
@@ -969,10 +969,10 @@
         <v>36</v>
       </c>
       <c r="H8" s="1">
-        <v>1.439</v>
+        <v>1.54</v>
       </c>
       <c r="I8" s="1">
-        <v>59.762</v>
+        <v>63.956</v>
       </c>
       <c r="J8" s="1">
         <v>1.57</v>
@@ -1013,10 +1013,10 @@
         <v>36</v>
       </c>
       <c r="H9" s="1">
-        <v>1.708</v>
+        <v>1.82</v>
       </c>
       <c r="I9" s="1">
-        <v>209.384</v>
+        <v>223.114</v>
       </c>
       <c r="J9" s="1">
         <v>1.85</v>
@@ -1057,10 +1057,10 @@
         <v>36</v>
       </c>
       <c r="H10" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I10" s="1">
-        <v>200.521</v>
+        <v>212.303</v>
       </c>
       <c r="J10" s="1">
         <v>1.85</v>
@@ -1101,10 +1101,10 @@
         <v>36</v>
       </c>
       <c r="H11" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I11" s="1">
-        <v>23.592</v>
+        <v>15.49</v>
       </c>
       <c r="J11" s="1">
         <v>0.66</v>
@@ -1145,10 +1145,10 @@
         <v>36</v>
       </c>
       <c r="H12" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I12" s="1">
-        <v>204.974</v>
+        <v>217.017</v>
       </c>
       <c r="J12" s="1">
         <v>1.85</v>
@@ -1189,10 +1189,10 @@
         <v>36</v>
       </c>
       <c r="H13" s="1">
-        <v>1.719</v>
+        <v>1.81</v>
       </c>
       <c r="I13" s="1">
-        <v>203.083</v>
+        <v>213.833</v>
       </c>
       <c r="J13" s="1">
         <v>1.84</v>
@@ -1251,10 +1251,10 @@
         <v>6</v>
       </c>
       <c r="D18" s="9">
-        <v>1.71048</v>
+        <v>1.81672</v>
       </c>
       <c r="E18" s="7">
-        <v>1207.63</v>
+        <v>1282.64</v>
       </c>
       <c r="F18" s="7">
         <v>1303.82</v>
@@ -1271,10 +1271,10 @@
         <v>5</v>
       </c>
       <c r="D19" s="9">
-        <v>1.42739</v>
+        <v>1.5356</v>
       </c>
       <c r="E19" s="7">
-        <v>251.42</v>
+        <v>270.48</v>
       </c>
       <c r="F19" s="7">
         <v>275.76</v>
@@ -1291,10 +1291,10 @@
         <v>1</v>
       </c>
       <c r="D20" s="9">
-        <v>0.9900099999999999</v>
+        <v>0.65002</v>
       </c>
       <c r="E20" s="7">
-        <v>23.59</v>
+        <v>15.49</v>
       </c>
       <c r="F20" s="7">
         <v>15.73</v>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="D21" s="9"/>
       <c r="E21" s="11">
-        <v>1482.64</v>
+        <v>1568.61</v>
       </c>
       <c r="F21" s="11">
         <v>1595.31</v>
